--- a/autoprogram/workbooks/input_values.xlsx
+++ b/autoprogram/workbooks/input_values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alessandro\projects\autoprogram\autoprogram\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC82C461-4356-4DDE-80CC-4603372314DA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE5F824-C2F7-472E-8F5C-11252F60A20D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4FBC6C86-D509-43E8-82AC-DBC3FF078B39}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="140">
   <si>
     <t>Auxiliary.Helix Angle</t>
   </si>
@@ -183,9 +183,6 @@
     <t>val_name</t>
   </si>
   <si>
-    <t>pippo</t>
-  </si>
-  <si>
     <t>val_addr</t>
   </si>
   <si>
@@ -201,13 +198,262 @@
     <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes1.diamEdge.fluteLength</t>
   </si>
   <si>
-    <t>Rollomatic.LibCurve.Data.Curves.ToolProfileCurve@D0</t>
-  </si>
-  <si>
     <t>a</t>
   </si>
   <si>
-    <t>b</t>
+    <t>Rollomatic.LibCurve.Data.Curves.ToolProfileCurve-D0</t>
+  </si>
+  <si>
+    <t>reference length (RL)</t>
+  </si>
+  <si>
+    <t>end stock removal (dL)</t>
+  </si>
+  <si>
+    <t>feed coeff. for dry run</t>
+  </si>
+  <si>
+    <t>cutting security distance</t>
+  </si>
+  <si>
+    <t>fast security distance</t>
+  </si>
+  <si>
+    <t>general feed out</t>
+  </si>
+  <si>
+    <t>drill diameter</t>
+  </si>
+  <si>
+    <t>first cutting length</t>
+  </si>
+  <si>
+    <t>program point angle</t>
+  </si>
+  <si>
+    <t>first diameter conicity</t>
+  </si>
+  <si>
+    <t>straightness diameter</t>
+  </si>
+  <si>
+    <t>blank first diameter</t>
+  </si>
+  <si>
+    <t>blank overall length</t>
+  </si>
+  <si>
+    <t>blank first step length (from the probing reference)</t>
+  </si>
+  <si>
+    <t>blank first step total angle</t>
+  </si>
+  <si>
+    <t>blank second diameter</t>
+  </si>
+  <si>
+    <t>blank first diameter conicity</t>
+  </si>
+  <si>
+    <t>blank second diameter conicity</t>
+  </si>
+  <si>
+    <t>flute 1 length</t>
+  </si>
+  <si>
+    <t>flute 1 helix angle</t>
+  </si>
+  <si>
+    <t>flute 1 lead</t>
+  </si>
+  <si>
+    <t>core diameter in mm</t>
+  </si>
+  <si>
+    <t>core diameter in %</t>
+  </si>
+  <si>
+    <t>rake angle</t>
+  </si>
+  <si>
+    <t>attack angle</t>
+  </si>
+  <si>
+    <t>measure distance</t>
+  </si>
+  <si>
+    <t>circular land width</t>
+  </si>
+  <si>
+    <t>feedrate</t>
+  </si>
+  <si>
+    <t>feedrate in</t>
+  </si>
+  <si>
+    <t>feedrate along sweep</t>
+  </si>
+  <si>
+    <t>number of repetitions</t>
+  </si>
+  <si>
+    <t>margin width</t>
+  </si>
+  <si>
+    <t>first cutting length (from the tip)</t>
+  </si>
+  <si>
+    <t>first relief</t>
+  </si>
+  <si>
+    <t>blank first step half angle</t>
+  </si>
+  <si>
+    <t>blank second step length (from the probing reference)</t>
+  </si>
+  <si>
+    <t>flute 1001 length</t>
+  </si>
+  <si>
+    <t>flute 1001 lead</t>
+  </si>
+  <si>
+    <t>OD clearance 1 setting angle</t>
+  </si>
+  <si>
+    <t>helix angle</t>
+  </si>
+  <si>
+    <t>cutting speed</t>
+  </si>
+  <si>
+    <t>m_tool.rL</t>
+  </si>
+  <si>
+    <t>m_tool.dL</t>
+  </si>
+  <si>
+    <t>m_tool.coeffDryRun</t>
+  </si>
+  <si>
+    <t>one_tooth.progStartBefore</t>
+  </si>
+  <si>
+    <t>one_tooth.progEndAfter</t>
+  </si>
+  <si>
+    <t>one_tooth.progF1Out</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.frontEdgeLimit</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes1.helix.func_helix_angle</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes1.helix.func_lead</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes1.flute.flute_op.flute_op.flute_one_multi.flute_one_multi1.core.coreFunctionAbsolute</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes1.flute.flute_op.flute_op.flute_one_multi.flute_one_multi1.core.coreFunction</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes1.flute.flute_op.flute_op.flute_one_multi.flute_one_multi1.flute_Simple_Ext_.flute_Lw_X.flute_Simple_Choices.func_rake_angle</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes1.flute.flute_op.flute_op.flute_one_multi.flute_one_multi1.flute_Simple_Ext_.flute_Lw_X.flute_Simple_Choices.attackAngle</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes1.flute.flute_op.flute_op.flute_one_multi.flute_one_multi1.flute_Simple_Ext_.flute_Lw_X.flute_Simple_Choices.pourcent_rake_in</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes1.flute.flute_op.flute_op.flute_one_multi.flute_one_multi1.flute_Simple_Ext_.flute_Lw_X.flute_Simple_Choices.circ_land_width</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes1.flute.flute_op.flute_op.flute_one_multi.flute_one_multi1.postpro.Feed</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.point.drill_straightgash_group.drill_straightgash_group.drill_straightgash_group.gash_one_multi.gash_one_multi1.straightgash.postpro.FeedInGash</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.point.drill_straightgash_group.drill_straightgash_group.drill_straightgash_group.gash_one_multi.gash_one_multi1.straightgash.postpro.FeedGashSweep</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.point.endrelief_from_attribute.oneAttribute.oneAttribute1.od_relief.multi_relief_allmulti.multi_relief.multi_relief1.rel_intern.relief_op_complete.relief_op_complete1.postpro.FeedIn</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.point.endrelief_from_attribute.oneAttribute.oneAttribute1.od_relief.multi_relief_allmulti.multi_relief.multi_relief1.rel_intern.relief_op_complete.relief_op_complete1.postpro.Feed</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.drillOD.drillOD1.od_relief.nbrRelief</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.drillOD.drillOD1.od_relief.od_relief.reliefs.reliefs1.margin_start</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.drillOD.drillOD1.od_relief.od_relief.reliefs.reliefs2.margin_start</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.drillOD.drillOD1.od_relief.od_relief.reliefs.reliefs3.margin_start</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.point.endrelief_from_attribute.oneAttribute.oneAttribute1.od_relief.multi_relief_allmulti.multi_relief.multi_relief1.rel_intern.relief_op_complete.relief_op_complete1.normal_field.func_relief_angle</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes2.diamEdge.fluteLength</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes2.helix.func_lead</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.drillOD.drillOD1.od_relief.od_relief.reliefs.reliefs1.od_relief.od_relief.od_reliefs.od_reliefs1.od_relief.relief.func_settingAngle</t>
+  </si>
+  <si>
+    <t>one_tooth.all_teeth.drill_type.drill_type1.n_Types.allFlute.flutes.flutes1.flute.flute_op.flute_op.flute_one_multi.flute_one_multi1.postpro.Vs</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.ToolProfileCurve-sP1</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.ToolProfileCurve-pA</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.ToolProfileCurve-Ta0</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.BlankProfileCurve-D0</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.BlankProfileCurve-L</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.BlankProfileCurve-sP1</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.BlankProfileCurve-sA1</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.BlankProfileCurve-D1</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.BlankProfileCurve-Ta0</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.BlankProfileCurve-Ta1</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.BlankProfileCurve-sP2</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.BlankProfileCurve-sA2</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.ToolProfileCurve-D0_TN</t>
+  </si>
+  <si>
+    <t>Rollomatic.LibCurve.Data.Curves.ToolProfileCurve-pA_TN</t>
   </si>
 </sst>
 </file>
@@ -272,7 +518,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -280,8 +526,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -601,563 +853,548 @@
   <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="90.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="52.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="1" max="1" width="90.42578125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="53.7109375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>51</v>
+      <c r="C1" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
+      <c r="B3" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
+      <c r="B4" s="4" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
+      <c r="B5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="1">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
+      <c r="B6" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="1">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
+      <c r="B7" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="1">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
+      <c r="B8" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="1">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
+      <c r="B9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>2</v>
+      <c r="B10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="1">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
+      <c r="B11" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="1">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
+      <c r="B12" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="1">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
+      <c r="B13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="A14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C14">
-        <v>2</v>
+      <c r="C14" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="1">
-        <v>1</v>
-      </c>
-      <c r="C15">
-        <v>2</v>
+      <c r="A15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="1">
-        <v>1</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
+      <c r="A16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="1">
-        <v>1</v>
-      </c>
-      <c r="C17">
-        <v>2</v>
+      <c r="A17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="1">
-        <v>1</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
+      <c r="A18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="1">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>2</v>
+      <c r="A19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="1">
-        <v>1</v>
-      </c>
-      <c r="C20">
-        <v>2</v>
+      <c r="A20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="1">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>2</v>
+      <c r="A21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="1">
-        <v>1</v>
-      </c>
-      <c r="C22">
-        <v>2</v>
+      <c r="A22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="1">
-        <v>1</v>
-      </c>
-      <c r="C23">
-        <v>2</v>
+      <c r="A23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="1">
-        <v>1</v>
-      </c>
-      <c r="C24">
-        <v>2</v>
+      <c r="A24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25">
-        <v>2</v>
+      <c r="A25" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="1" t="s">
+      <c r="A26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C50" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="1">
-        <v>1</v>
-      </c>
-      <c r="C27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="1">
-        <v>1</v>
-      </c>
-      <c r="C28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="1">
-        <v>1</v>
-      </c>
-      <c r="C29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" s="1">
-        <v>1</v>
-      </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B32" s="1">
-        <v>1</v>
-      </c>
-      <c r="C32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B33" s="1">
-        <v>1</v>
-      </c>
-      <c r="C33">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B34" s="1">
-        <v>1</v>
-      </c>
-      <c r="C34">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" s="1">
-        <v>1</v>
-      </c>
-      <c r="C35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B36" s="1">
-        <v>1</v>
-      </c>
-      <c r="C36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B37" s="1">
-        <v>1</v>
-      </c>
-      <c r="C37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" s="1">
-        <v>1</v>
-      </c>
-      <c r="C38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39" s="1">
-        <v>1</v>
-      </c>
-      <c r="C39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="1">
-        <v>1</v>
-      </c>
-      <c r="C40">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="1">
-        <v>1</v>
-      </c>
-      <c r="C41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B42" s="1">
-        <v>1</v>
-      </c>
-      <c r="C42">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" s="1">
-        <v>1</v>
-      </c>
-      <c r="C43">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="1">
-        <v>1</v>
-      </c>
-      <c r="C44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="1">
-        <v>1</v>
-      </c>
-      <c r="C45">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B46" s="1">
-        <v>1</v>
-      </c>
-      <c r="C46">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B47" s="1">
-        <v>1</v>
-      </c>
-      <c r="C47">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B48" s="1">
-        <v>1</v>
-      </c>
-      <c r="C48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B49" s="1">
-        <v>1</v>
-      </c>
-      <c r="C49">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C50">
-        <v>2</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C49">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C50">
     <sortCondition ref="A1"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1180,7 +1417,7 @@
         <v>48</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1188,7 +1425,7 @@
         <v>28</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
